--- a/content/blog/oscar-idades/dados_para_adicionar_data.xlsx
+++ b/content/blog/oscar-idades/dados_para_adicionar_data.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernandafperes/Documents/Estatística/Estudos/Oscars/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernandafperes/Documents/Blog_/content/blog/oscar-idades/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566A13D8-E9D5-4C48-9285-4094DF9CFD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEEE5D6C-3267-534B-B8E3-C2C1DCD2DA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="28560" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="28560" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="112">
   <si>
     <t>year_film</t>
   </si>
@@ -332,6 +345,30 @@
   </si>
   <si>
     <t>Adrien Brody</t>
+  </si>
+  <si>
+    <t>Michael B. Jordan</t>
+  </si>
+  <si>
+    <t>Sinners</t>
+  </si>
+  <si>
+    <t>Sean Penn</t>
+  </si>
+  <si>
+    <t>One Battle After Another</t>
+  </si>
+  <si>
+    <t>Amy Madigan</t>
+  </si>
+  <si>
+    <t>The Hour of Evil</t>
+  </si>
+  <si>
+    <t>Jessie Buckley</t>
+  </si>
+  <si>
+    <t>Hamnet</t>
   </si>
 </sst>
 </file>
@@ -375,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -383,14 +420,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -699,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -738,1333 +769,1359 @@
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>2024</v>
-      </c>
-      <c r="B2" s="4">
         <v>2025</v>
       </c>
+      <c r="B2" s="3">
+        <v>2026</v>
+      </c>
       <c r="C2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H2" s="5">
-        <v>26768</v>
+      <c r="H2" s="4">
+        <v>31817</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>2024</v>
-      </c>
-      <c r="B3" s="4">
         <v>2025</v>
       </c>
+      <c r="B3" s="3">
+        <v>2026</v>
+      </c>
       <c r="C3">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H3" s="5">
-        <v>30224</v>
+      <c r="H3" s="4">
+        <v>22145</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>2024</v>
-      </c>
-      <c r="B4" s="4">
         <v>2025</v>
       </c>
+      <c r="B4" s="3">
+        <v>2026</v>
+      </c>
       <c r="C4">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H4" s="5">
-        <v>36244</v>
+      <c r="H4" s="4">
+        <v>32870</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>2024</v>
-      </c>
-      <c r="B5" s="4">
         <v>2025</v>
       </c>
+      <c r="B5" s="3">
+        <v>2026</v>
+      </c>
       <c r="C5">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" s="4">
+        <v>18517</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2024</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C6">
         <v>97</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H5" s="5">
-        <v>28660</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2023</v>
-      </c>
-      <c r="B6">
-        <v>2024</v>
-      </c>
-      <c r="C6">
-        <v>96</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H6" s="5">
-        <v>27905</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="4">
+        <v>26768</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>2023</v>
-      </c>
-      <c r="B7">
         <v>2024</v>
       </c>
+      <c r="B7" s="3">
+        <v>2025</v>
+      </c>
       <c r="C7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H7" s="5">
-        <v>23836</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="4">
+        <v>30224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>2023</v>
-      </c>
-      <c r="B8">
         <v>2024</v>
       </c>
+      <c r="B8" s="3">
+        <v>2025</v>
+      </c>
       <c r="C8">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="5">
-        <v>32453</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="4">
+        <v>36244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>2023</v>
-      </c>
-      <c r="B9">
         <v>2024</v>
       </c>
+      <c r="B9" s="3">
+        <v>2025</v>
+      </c>
       <c r="C9">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H9" s="5">
-        <v>31553</v>
+      <c r="H9" s="4">
+        <v>28660</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B10">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C10">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F10" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H10" s="6">
-        <v>25175</v>
+      <c r="H10" s="4">
+        <v>27905</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C11">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H11" s="5">
-        <v>26165</v>
+      <c r="H11" s="4">
+        <v>23836</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B12">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C12">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H12" s="5">
-        <v>22864</v>
+      <c r="H12" s="4">
+        <v>32453</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B13">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C13">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H13" s="5">
-        <v>21511</v>
+      <c r="H13" s="4">
+        <v>31553</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B14">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C14">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H14" s="5">
-        <v>25106</v>
+      <c r="H14" s="4">
+        <v>25175</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B15">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C15">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H15" s="5">
-        <v>25043</v>
+      <c r="H15" s="4">
+        <v>26165</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B16">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C16">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H16" s="5">
-        <v>28208</v>
+      <c r="H16" s="4">
+        <v>22864</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B17">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C17">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H17" s="5">
-        <v>33263</v>
+      <c r="H17" s="4">
+        <v>21511</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B18">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C18">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H18" s="5">
-        <v>32563</v>
+      <c r="H18" s="4">
+        <v>25106</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B19">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C19">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H19" s="5">
-        <v>17337</v>
+      <c r="H19" s="4">
+        <v>25043</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="B20">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C20">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H20" s="5">
-        <v>27330</v>
+      <c r="H20" s="4">
+        <v>28208</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="B21">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C21">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H21" s="5">
-        <v>23363</v>
+      <c r="H21" s="4">
+        <v>33263</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B22">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="F22" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H22" s="5">
-        <v>25318</v>
+      <c r="H22" s="4">
+        <v>32563</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B23">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C23">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
         <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H23" s="5">
-        <v>24513</v>
+      <c r="H23" s="4">
+        <v>17337</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B24">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C24">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H24" s="5">
-        <v>29718</v>
+      <c r="H24" s="4">
+        <v>27330</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B25">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C25">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
         <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H25" s="5">
-        <v>27076</v>
+      <c r="H25" s="4">
+        <v>23363</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B26">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C26">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
         <v>22</v>
       </c>
       <c r="E26" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H26" s="5">
-        <v>27059</v>
+      <c r="H26" s="4">
+        <v>25318</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B27">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C27">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
         <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H27" s="5">
-        <v>25948</v>
+      <c r="H27" s="4">
+        <v>24513</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B28">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C28">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
         <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H28" s="5">
-        <v>21265</v>
+      <c r="H28" s="4">
+        <v>29718</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B29">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C29">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
         <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H29" s="5">
-        <v>25147</v>
+      <c r="H29" s="4">
+        <v>27076</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B30">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C30">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E30" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F30" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H30" s="5">
-        <v>21873</v>
+      <c r="H30" s="4">
+        <v>27059</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B31">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C31">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="F31" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H31" s="5">
-        <v>27618</v>
+      <c r="H31" s="4">
+        <v>25948</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B32">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C32">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H32" s="5">
-        <v>27076</v>
+      <c r="H32" s="4">
+        <v>21265</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B33">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C33">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H33" s="5">
-        <v>32453</v>
+      <c r="H33" s="4">
+        <v>25147</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B34">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C34">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D34" t="s">
         <v>16</v>
       </c>
       <c r="E34" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F34" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H34" s="5">
-        <v>23965</v>
+      <c r="H34" s="4">
+        <v>21873</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B35">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C35">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D35" t="s">
         <v>19</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F35" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H35" s="5">
-        <v>27344</v>
+      <c r="H35" s="4">
+        <v>27618</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B36">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C36">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
         <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F36" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H36" s="5">
-        <v>21933</v>
+      <c r="H36" s="4">
+        <v>27076</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B37">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C37">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D37" t="s">
         <v>22</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F37" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H37" s="5">
-        <v>32782</v>
+      <c r="H37" s="4">
+        <v>32453</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B38">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C38">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D38" t="s">
         <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F38" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H38" s="5">
-        <v>32419</v>
+      <c r="H38" s="4">
+        <v>23965</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B39">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C39">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
         <v>19</v>
       </c>
       <c r="E39" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F39" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H39" s="5">
-        <v>29957</v>
+      <c r="H39" s="4">
+        <v>27344</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B40">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C40">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F40" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H40" s="5">
-        <v>20098</v>
+      <c r="H40" s="4">
+        <v>21933</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B41">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C41">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
         <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F41" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H41" s="5">
-        <v>22253</v>
+      <c r="H41" s="4">
+        <v>32782</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B42">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C42">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
         <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F42" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H42" s="5">
-        <v>24936</v>
+      <c r="H42" s="4">
+        <v>32419</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="B43">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="C43">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H43" s="5">
-        <v>27147</v>
+      <c r="H43" s="4">
+        <v>29957</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>2003</v>
+        <v>2014</v>
       </c>
       <c r="B44">
-        <v>2004</v>
+        <v>2015</v>
       </c>
       <c r="C44">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F44" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H44" s="5">
-        <v>25318</v>
+      <c r="H44" s="4">
+        <v>20098</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>1989</v>
+        <v>2014</v>
       </c>
       <c r="B45">
-        <v>1990</v>
+        <v>2015</v>
       </c>
       <c r="C45">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F45" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H45" s="5">
-        <v>20939</v>
+      <c r="H45" s="4">
+        <v>22253</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>1982</v>
+        <v>2014</v>
       </c>
       <c r="B46">
-        <v>1983</v>
+        <v>2015</v>
       </c>
       <c r="C46">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H46" s="5">
-        <v>13297</v>
+      <c r="H46" s="4">
+        <v>24936</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>1962</v>
+        <v>2008</v>
       </c>
       <c r="B47">
-        <v>1963</v>
+        <v>2009</v>
       </c>
       <c r="C47">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="D47" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F47" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H47" s="5">
-        <v>450</v>
+      <c r="H47" s="4">
+        <v>27147</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>1950</v>
+        <v>2003</v>
       </c>
       <c r="B48">
-        <v>1951</v>
+        <v>2004</v>
       </c>
       <c r="C48">
+        <v>76</v>
+      </c>
+      <c r="D48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" t="s">
         <v>23</v>
       </c>
-      <c r="D48" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" t="s">
-        <v>11</v>
-      </c>
       <c r="F48" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H48" s="5">
-        <v>4391</v>
+      <c r="H48" s="4">
+        <v>25318</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49">
+        <v>1989</v>
+      </c>
+      <c r="B49">
+        <v>1990</v>
+      </c>
+      <c r="C49">
+        <v>62</v>
+      </c>
+      <c r="D49" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H49" s="4">
+        <v>20939</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>1982</v>
+      </c>
+      <c r="B50">
+        <v>1983</v>
+      </c>
+      <c r="C50">
+        <v>55</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H50" s="4">
+        <v>13297</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>1962</v>
+      </c>
+      <c r="B51">
+        <v>1963</v>
+      </c>
+      <c r="C51">
+        <v>35</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H51" s="4">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>1950</v>
+      </c>
+      <c r="B52">
+        <v>1951</v>
+      </c>
+      <c r="C52">
+        <v>23</v>
+      </c>
+      <c r="D52" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H52" s="4">
+        <v>4391</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53">
         <v>1940</v>
       </c>
-      <c r="B49">
+      <c r="B53">
         <v>1941</v>
       </c>
-      <c r="C49">
+      <c r="C53">
         <v>13</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D53" t="s">
         <v>8</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E53" t="s">
         <v>9</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F53" t="s">
         <v>10</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H49" s="5">
+      <c r="G53" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H53" s="4">
         <v>3063</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H50" s="3"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H52" s="3"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H53" s="3"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H54" s="3"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H55" s="3"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H56" s="3"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H58" s="3"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H59" s="3"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H60" s="3"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H61" s="3"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H62" s="3"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H63" s="3"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="H64" s="3"/>
-    </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H65" s="3"/>
-    </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H66" s="3"/>
-    </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H67" s="3"/>
-    </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H68" s="3"/>
-    </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H69" s="3"/>
-    </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H70" s="3"/>
-    </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H71" s="3"/>
-    </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H72" s="3"/>
-    </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H73" s="3"/>
-    </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H74" s="3"/>
-    </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H75" s="3"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H75">
-    <sortCondition descending="1" ref="B1:B75"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:H79">
+    <sortCondition descending="1" ref="B1:B79"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
